--- a/data/dividends_info_20260521.xlsx
+++ b/data/dividends_info_20260521.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55.97999954223633</v>
+        <v>55.08000183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1607717054947382</v>
+        <v>0.1633986873785052</v>
       </c>
       <c r="J2" t="n">
         <v>298</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.54999923706055</v>
+        <v>55.15000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.260126029908188</v>
+        <v>1.26926560404813</v>
       </c>
       <c r="J3" t="n">
         <v>277</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.079999923706055</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6607929570941081</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>207</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>55.97999954223633</v>
+        <v>55.08000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1607717054947382</v>
+        <v>0.1633986873785052</v>
       </c>
       <c r="J6" t="n">
         <v>207</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.055000066757202</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.746958515748678</v>
       </c>
       <c r="J7" t="n">
         <v>186</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.67000007629395</v>
+        <v>23.79000091552734</v>
       </c>
       <c r="I8" t="n">
-        <v>1.140684406969695</v>
+        <v>1.13493059945103</v>
       </c>
       <c r="J8" t="n">
         <v>186</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.800000190734863</v>
+        <v>6.849999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8823529164271378</v>
+        <v>0.8759124209537983</v>
       </c>
       <c r="J10" t="n">
         <v>151</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.460000038146973</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9157509093529076</v>
+        <v>0.9469696593405037</v>
       </c>
       <c r="J12" t="n">
         <v>137</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J13" t="n">
         <v>130</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.67000007629395</v>
+        <v>23.79000091552734</v>
       </c>
       <c r="I14" t="n">
-        <v>1.140684406969695</v>
+        <v>1.13493059945103</v>
       </c>
       <c r="J14" t="n">
         <v>123</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>55.97999954223633</v>
+        <v>55.08000183105469</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1607717054947382</v>
+        <v>0.1633986873785052</v>
       </c>
       <c r="J15" t="n">
         <v>123</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.380000114440918</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="I16" t="n">
-        <v>6.849314889533817</v>
+        <v>6.772009291759015</v>
       </c>
       <c r="J16" t="n">
         <v>116</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J18" t="n">
         <v>74</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.889999866485596</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>4.244482269388714</v>
+        <v>4.230118552532127</v>
       </c>
       <c r="J19" t="n">
         <v>67</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.746999740600586</v>
+        <v>9.760000228881836</v>
       </c>
       <c r="I20" t="n">
-        <v>2.667487503020898</v>
+        <v>2.663934363757563</v>
       </c>
       <c r="J20" t="n">
         <v>60</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14.92000007629395</v>
+        <v>14.77999973297119</v>
       </c>
       <c r="I21" t="n">
-        <v>4.02144770061581</v>
+        <v>4.059539992152512</v>
       </c>
       <c r="J21" t="n">
         <v>60</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.618000030517578</v>
+        <v>3.624000072479248</v>
       </c>
       <c r="I22" t="n">
-        <v>6.080707521954542</v>
+        <v>6.0706400551889</v>
       </c>
       <c r="J22" t="n">
         <v>60</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.070000171661377</v>
+        <v>6.065000057220459</v>
       </c>
       <c r="I24" t="n">
-        <v>3.953871387359636</v>
+        <v>3.957131042633329</v>
       </c>
       <c r="J24" t="n">
         <v>60</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18.5</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>2.032432432432433</v>
+        <v>2.106442532014339</v>
       </c>
       <c r="J25" t="n">
         <v>60</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.255000114440918</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I26" t="n">
-        <v>2.820211440012318</v>
+        <v>2.898550818115528</v>
       </c>
       <c r="J26" t="n">
         <v>53</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.700000047683716</v>
+        <v>2.660000085830688</v>
       </c>
       <c r="I28" t="n">
-        <v>5.555555457440915</v>
+        <v>5.639097562403148</v>
       </c>
       <c r="J28" t="n">
         <v>53</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.179999828338623</v>
+        <v>4.440000057220459</v>
       </c>
       <c r="I30" t="n">
-        <v>1.674641217098378</v>
+        <v>1.576576556258461</v>
       </c>
       <c r="J30" t="n">
         <v>46</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>31.20000076293945</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4807692190128909</v>
+        <v>0.4862236568726221</v>
       </c>
       <c r="J31" t="n">
         <v>46</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23.21999931335449</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="I33" t="n">
-        <v>4.091300723913577</v>
+        <v>4.077253352390448</v>
       </c>
       <c r="J33" t="n">
         <v>32</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30.79999923706055</v>
+        <v>29.85000038146973</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6331168987996708</v>
+        <v>0.6532663233098384</v>
       </c>
       <c r="J34" t="n">
         <v>32</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.820000052452087</v>
+        <v>1.830000042915344</v>
       </c>
       <c r="I35" t="n">
-        <v>1.813186760931082</v>
+        <v>1.803278646235889</v>
       </c>
       <c r="J35" t="n">
         <v>32</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.289999961853027</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="I36" t="n">
-        <v>5.482041627433514</v>
+        <v>5.566218769225643</v>
       </c>
       <c r="J36" t="n">
         <v>32</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.904000043869019</v>
+        <v>3.888000011444092</v>
       </c>
       <c r="I37" t="n">
-        <v>4.098360609684668</v>
+        <v>4.115226325335641</v>
       </c>
       <c r="J37" t="n">
         <v>32</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.746000051498413</v>
+        <v>2.727999925613403</v>
       </c>
       <c r="I38" t="n">
-        <v>5.047341493106308</v>
+        <v>5.080645299828414</v>
       </c>
       <c r="J38" t="n">
         <v>32</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>52.08000183105469</v>
+        <v>51.34999847412109</v>
       </c>
       <c r="I39" t="n">
-        <v>1.209677376824396</v>
+        <v>1.226874427888253</v>
       </c>
       <c r="J39" t="n">
         <v>32</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>5.349999904632568</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="I40" t="n">
-        <v>2.616822476553204</v>
+        <v>2.65151504615341</v>
       </c>
       <c r="J40" t="n">
         <v>32</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.29999923706055</v>
+        <v>19.39999961853027</v>
       </c>
       <c r="I41" t="n">
-        <v>4.041450936962817</v>
+        <v>4.020618635760015</v>
       </c>
       <c r="J41" t="n">
         <v>32</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24.95000076293945</v>
+        <v>24.80999946594238</v>
       </c>
       <c r="I42" t="n">
-        <v>3.406813523078459</v>
+        <v>3.426037961696963</v>
       </c>
       <c r="J42" t="n">
         <v>32</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>55.9900016784668</v>
+        <v>55.08000183105469</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1607429850008615</v>
+        <v>0.1633986873785052</v>
       </c>
       <c r="J43" t="n">
         <v>32</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.409999966621399</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I44" t="n">
-        <v>0.709219874945225</v>
+        <v>0.7194244678355752</v>
       </c>
       <c r="J44" t="n">
         <v>32</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.368000030517578</v>
+        <v>6.395999908447266</v>
       </c>
       <c r="I45" t="n">
-        <v>2.847047725049466</v>
+        <v>2.83458415564633</v>
       </c>
       <c r="J45" t="n">
         <v>32</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.659999847412109</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I46" t="n">
-        <v>3.002309521722411</v>
+        <v>3.023255679851103</v>
       </c>
       <c r="J46" t="n">
         <v>32</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>10.04500007629395</v>
+        <v>10.06999969482422</v>
       </c>
       <c r="I47" t="n">
-        <v>2.757590820270037</v>
+        <v>2.750744869857072</v>
       </c>
       <c r="J47" t="n">
         <v>32</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.154999971389771</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I48" t="n">
-        <v>1.168831197784008</v>
+        <v>1.163793136936023</v>
       </c>
       <c r="J48" t="n">
         <v>25</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.075999975204468</v>
+        <v>3.038000106811523</v>
       </c>
       <c r="I49" t="n">
-        <v>3.576072850673157</v>
+        <v>3.620803032671663</v>
       </c>
       <c r="J49" t="n">
         <v>25</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>1.176470610234702</v>
       </c>
       <c r="J50" t="n">
         <v>25</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.224999904632568</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="I51" t="n">
-        <v>4.961240456787833</v>
+        <v>4.907975474480399</v>
       </c>
       <c r="J51" t="n">
         <v>18</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8899999856948853</v>
+        <v>0.8949999809265137</v>
       </c>
       <c r="I52" t="n">
-        <v>2.808988809194278</v>
+        <v>2.79329614891385</v>
       </c>
       <c r="J52" t="n">
         <v>18</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>28.64999961853027</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="I53" t="n">
-        <v>3.874345601324452</v>
+        <v>3.901581617691721</v>
       </c>
       <c r="J53" t="n">
         <v>14</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8650000095367432</v>
+        <v>0.8579999804496765</v>
       </c>
       <c r="I54" t="n">
-        <v>3.468208054248081</v>
+        <v>3.496503576174564</v>
       </c>
       <c r="J54" t="n">
         <v>11</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.5109999775886536</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I55" t="n">
-        <v>4.500978670984329</v>
+        <v>4.509804005899691</v>
       </c>
       <c r="J55" t="n">
         <v>11</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>19.60000038146973</v>
+        <v>19.64999961853027</v>
       </c>
       <c r="I56" t="n">
-        <v>3.061224430216099</v>
+        <v>3.053435173780819</v>
       </c>
       <c r="J56" t="n">
         <v>11</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.529999971389771</v>
+        <v>2.515000104904175</v>
       </c>
       <c r="I58" t="n">
-        <v>7.114624586383811</v>
+        <v>7.157057355544653</v>
       </c>
       <c r="J58" t="n">
         <v>4</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.100000381469727</v>
+        <v>8.25</v>
       </c>
       <c r="I59" t="n">
-        <v>3.703703529277682</v>
+        <v>3.636363636363636</v>
       </c>
       <c r="J59" t="n">
         <v>4</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15</v>
+        <v>14.72000026702881</v>
       </c>
       <c r="I60" t="n">
-        <v>1.666666666666667</v>
+        <v>1.698369534408044</v>
       </c>
       <c r="J60" t="n">
         <v>4</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.440000057220459</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8720930087495459</v>
+        <v>0.8695652053727246</v>
       </c>
       <c r="J61" t="n">
         <v>4</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.179999828338623</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="I62" t="n">
-        <v>3.588516893782237</v>
+        <v>3.640776800158699</v>
       </c>
       <c r="J62" t="n">
         <v>4</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="I63" t="n">
-        <v>4.070175438596491</v>
+        <v>4.142857142857142</v>
       </c>
       <c r="J63" t="n">
         <v>4</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.282000064849854</v>
+        <v>2.280999898910522</v>
       </c>
       <c r="I64" t="n">
-        <v>4.55740565488734</v>
+        <v>4.559403972340099</v>
       </c>
       <c r="J64" t="n">
         <v>-3</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>10.72000026702881</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="I65" t="n">
-        <v>2.705223813211502</v>
+        <v>2.735848958146834</v>
       </c>
       <c r="J65" t="n">
         <v>-3</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2.045000076293945</v>
+        <v>2.055000066757202</v>
       </c>
       <c r="I66" t="n">
-        <v>3.765281033120711</v>
+        <v>3.746958515748678</v>
       </c>
       <c r="J66" t="n">
         <v>-3</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>38.36999893188477</v>
+        <v>38.58000183105469</v>
       </c>
       <c r="I67" t="n">
-        <v>4.27417264960409</v>
+        <v>4.250907004052793</v>
       </c>
       <c r="J67" t="n">
         <v>-3</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>35.08000183105469</v>
+        <v>34.72000122070312</v>
       </c>
       <c r="I68" t="n">
-        <v>5.701253978354965</v>
+        <v>5.760368461068555</v>
       </c>
       <c r="J68" t="n">
         <v>-3</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3.206000089645386</v>
+        <v>3.121999979019165</v>
       </c>
       <c r="I69" t="n">
-        <v>3.119151503550362</v>
+        <v>3.20307497347956</v>
       </c>
       <c r="J69" t="n">
         <v>-3</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>34.29999923706055</v>
+        <v>34.09999847412109</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4328279979656431</v>
+        <v>0.435366588396384</v>
       </c>
       <c r="J70" t="n">
         <v>-3</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.81999969482422</v>
+        <v>19.43000030517578</v>
       </c>
       <c r="I71" t="n">
-        <v>4.641776055325814</v>
+        <v>4.734945885486835</v>
       </c>
       <c r="J71" t="n">
         <v>-3</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10.32999992370605</v>
+        <v>10.38000011444092</v>
       </c>
       <c r="I72" t="n">
-        <v>2.904162654556634</v>
+        <v>2.890173378540068</v>
       </c>
       <c r="J72" t="n">
         <v>-3</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>84.12000274658203</v>
+        <v>83.48000335693359</v>
       </c>
       <c r="I73" t="n">
-        <v>1.236329013365679</v>
+        <v>1.245807328915998</v>
       </c>
       <c r="J73" t="n">
         <v>-3</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>43.95000076293945</v>
+        <v>43.61999893188477</v>
       </c>
       <c r="I74" t="n">
-        <v>1.592718971213922</v>
+        <v>1.604768494132913</v>
       </c>
       <c r="J74" t="n">
         <v>-3</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>55.54999923706055</v>
+        <v>55.15000152587891</v>
       </c>
       <c r="I75" t="n">
-        <v>3.960396093997164</v>
+        <v>3.989120469865553</v>
       </c>
       <c r="J75" t="n">
         <v>-3</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>8.666000366210938</v>
+        <v>8.564999580383301</v>
       </c>
       <c r="I76" t="n">
-        <v>9.923839876042152</v>
+        <v>10.04086447324161</v>
       </c>
       <c r="J76" t="n">
         <v>-3</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.57999992370605</v>
+        <v>11.44799995422363</v>
       </c>
       <c r="I77" t="n">
-        <v>4.83592403876958</v>
+        <v>4.891684156527213</v>
       </c>
       <c r="J77" t="n">
         <v>-3</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.180000066757202</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I78" t="n">
-        <v>1.834862329132901</v>
+        <v>1.826483970542351</v>
       </c>
       <c r="J78" t="n">
         <v>-3</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.859999656677246</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="I79" t="n">
-        <v>3.386004645879507</v>
+        <v>3.49243299966205</v>
       </c>
       <c r="J79" t="n">
         <v>-3</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>2.210000038146973</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I80" t="n">
-        <v>4.886877743701542</v>
+        <v>4.909090802689231</v>
       </c>
       <c r="J80" t="n">
         <v>-3</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>88.19999694824219</v>
+        <v>87.40000152587891</v>
       </c>
       <c r="I81" t="n">
-        <v>2.335600987842274</v>
+        <v>2.356979363884839</v>
       </c>
       <c r="J81" t="n">
         <v>-3</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>15.14000034332275</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="I82" t="n">
-        <v>4.95376474896036</v>
+        <v>4.960317497861329</v>
       </c>
       <c r="J82" t="n">
         <v>-3</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>13.57999992370605</v>
+        <v>13.51000022888184</v>
       </c>
       <c r="I83" t="n">
-        <v>2.209131087521599</v>
+        <v>2.220577312490761</v>
       </c>
       <c r="J83" t="n">
         <v>-3</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>50.59999847412109</v>
+        <v>50.20000076293945</v>
       </c>
       <c r="I84" t="n">
-        <v>1.679841947890027</v>
+        <v>1.693227065899806</v>
       </c>
       <c r="J84" t="n">
         <v>-3</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>34.84000015258789</v>
+        <v>34.18000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>2.439724443964626</v>
+        <v>2.486834383881754</v>
       </c>
       <c r="J85" t="n">
         <v>-3</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>66.80000305175781</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="I86" t="n">
-        <v>1.946107695523213</v>
+        <v>1.9938651239999</v>
       </c>
       <c r="J86" t="n">
         <v>-3</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.239999771118164</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I87" t="n">
-        <v>8.287293079670008</v>
+        <v>8.196721119254038</v>
       </c>
       <c r="J87" t="n">
         <v>-3</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.050000190734863</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I88" t="n">
-        <v>7.768594796406303</v>
+        <v>7.899159917083225</v>
       </c>
       <c r="J88" t="n">
         <v>-3</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.15999984741211</v>
+        <v>23.20000076293945</v>
       </c>
       <c r="I90" t="n">
-        <v>4.317789320329981</v>
+        <v>4.310344685839137</v>
       </c>
       <c r="J90" t="n">
         <v>-3</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>4.650000095367432</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="I91" t="n">
-        <v>4.623655819151359</v>
+        <v>4.673913140378064</v>
       </c>
       <c r="J91" t="n">
         <v>-3</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>23.67000007629395</v>
+        <v>23.79000091552734</v>
       </c>
       <c r="I92" t="n">
-        <v>1.140684406969695</v>
+        <v>1.13493059945103</v>
       </c>
       <c r="J92" t="n">
         <v>-3</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>9.680000305175781</v>
+        <v>9.439999580383301</v>
       </c>
       <c r="I93" t="n">
-        <v>2.066115637342102</v>
+        <v>2.118644161972296</v>
       </c>
       <c r="J93" t="n">
         <v>-3</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.375</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I94" t="n">
-        <v>2.865671641791045</v>
+        <v>2.891566198611749</v>
       </c>
       <c r="J94" t="n">
         <v>-3</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>21.02000045776367</v>
+        <v>20.84000015258789</v>
       </c>
       <c r="I95" t="n">
-        <v>3.758325322529743</v>
+        <v>3.790786920420913</v>
       </c>
       <c r="J95" t="n">
         <v>-3</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5.099999904632568</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I96" t="n">
-        <v>1.823529445863788</v>
+        <v>1.816406290599844</v>
       </c>
       <c r="J96" t="n">
         <v>-3</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.800000190734863</v>
+        <v>6.849999904632568</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8823529164271378</v>
+        <v>0.8759124209537983</v>
       </c>
       <c r="J97" t="n">
         <v>-3</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>34.70000076293945</v>
+        <v>34.59999847412109</v>
       </c>
       <c r="I98" t="n">
-        <v>1.008645510964396</v>
+        <v>1.011560738252</v>
       </c>
       <c r="J98" t="n">
         <v>-3</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.829999923706055</v>
+        <v>6.90500020980835</v>
       </c>
       <c r="I99" t="n">
-        <v>8.115666269279092</v>
+        <v>8.02751604862565</v>
       </c>
       <c r="J99" t="n">
         <v>-3</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>12.75</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I101" t="n">
-        <v>1.568627450980392</v>
+        <v>1.562499976716936</v>
       </c>
       <c r="J101" t="n">
         <v>-3</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>6.894999980926514</v>
+        <v>6.869999885559082</v>
       </c>
       <c r="I102" t="n">
-        <v>1.493836117257819</v>
+        <v>1.499272222937131</v>
       </c>
       <c r="J102" t="n">
         <v>-3</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5.664000034332275</v>
+        <v>5.596000194549561</v>
       </c>
       <c r="I103" t="n">
-        <v>3.354519753677914</v>
+        <v>3.395282226492018</v>
       </c>
       <c r="J103" t="n">
         <v>-3</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>10.06999969482422</v>
+        <v>10.13000011444092</v>
       </c>
       <c r="I104" t="n">
-        <v>4.289970338549658</v>
+        <v>4.264560662582404</v>
       </c>
       <c r="J104" t="n">
         <v>-3</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>25.35000038146973</v>
+        <v>25.07999992370605</v>
       </c>
       <c r="I105" t="n">
-        <v>1.735700171119642</v>
+        <v>1.754385970249164</v>
       </c>
       <c r="J105" t="n">
         <v>-3</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>7.489999771118164</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="I107" t="n">
-        <v>6.275033569591616</v>
+        <v>6.283422443870752</v>
       </c>
       <c r="J107" t="n">
         <v>-3</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>51.36000061035156</v>
+        <v>51.93999862670898</v>
       </c>
       <c r="I108" t="n">
-        <v>2.725856665425801</v>
+        <v>2.695417861024126</v>
       </c>
       <c r="J108" t="n">
         <v>-3</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.440999984741211</v>
+        <v>3.431999921798706</v>
       </c>
       <c r="I109" t="n">
-        <v>8.718395853830909</v>
+        <v>8.74125894043641</v>
       </c>
       <c r="J109" t="n">
         <v>-3</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>13.55000019073486</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8856088436223998</v>
+        <v>0.8955224135533352</v>
       </c>
       <c r="J110" t="n">
         <v>-3</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3.470000028610229</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I111" t="n">
-        <v>4.899135406292396</v>
+        <v>4.941860382914093</v>
       </c>
       <c r="J111" t="n">
         <v>-3</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>22.75</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I112" t="n">
-        <v>3.076923076923077</v>
+        <v>3.090507778319433</v>
       </c>
       <c r="J112" t="n">
         <v>-3</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.690000057220459</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="I114" t="n">
-        <v>5.799648447828024</v>
+        <v>5.820105741792094</v>
       </c>
       <c r="J114" t="n">
         <v>-3</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.8859999775886536</v>
+        <v>0.8930000066757202</v>
       </c>
       <c r="I115" t="n">
-        <v>7.90067740075036</v>
+        <v>7.838745742072482</v>
       </c>
       <c r="J115" t="n">
         <v>-3</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>51.25</v>
+        <v>51.70000076293945</v>
       </c>
       <c r="I116" t="n">
-        <v>1.385365853658537</v>
+        <v>1.373307523254342</v>
       </c>
       <c r="J116" t="n">
         <v>-3</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>104.0999984741211</v>
+        <v>103.9000015258789</v>
       </c>
       <c r="I117" t="n">
-        <v>1.296829990190255</v>
+        <v>1.299326256182729</v>
       </c>
       <c r="J117" t="n">
         <v>-3</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>7.380000114440918</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I118" t="n">
-        <v>1.084010823298754</v>
+        <v>1.11731845956554</v>
       </c>
       <c r="J118" t="n">
         <v>-3</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>4.329999923706055</v>
+        <v>4.322000026702881</v>
       </c>
       <c r="I120" t="n">
-        <v>3.926097066867768</v>
+        <v>3.933364158946748</v>
       </c>
       <c r="J120" t="n">
         <v>-3</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>57.70000076293945</v>
+        <v>57.09999847412109</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7798960035526269</v>
+        <v>0.7880910893613235</v>
       </c>
       <c r="J122" t="n">
         <v>-3</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.480000019073486</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7299270047587131</v>
+        <v>0.7490636490078573</v>
       </c>
       <c r="J123" t="n">
         <v>-3</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>37.41999816894531</v>
+        <v>36.93999862670898</v>
       </c>
       <c r="I124" t="n">
-        <v>2.805986240991829</v>
+        <v>2.842447317366198</v>
       </c>
       <c r="J124" t="n">
         <v>-3</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>20.94000053405762</v>
+        <v>20.13999938964844</v>
       </c>
       <c r="I126" t="n">
-        <v>1.814708645216859</v>
+        <v>1.886792510010266</v>
       </c>
       <c r="J126" t="n">
         <v>-3</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>26.15999984741211</v>
+        <v>26.65999984741211</v>
       </c>
       <c r="I127" t="n">
-        <v>2.293577995029519</v>
+        <v>2.250562653541208</v>
       </c>
       <c r="J127" t="n">
         <v>-3</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>35.25</v>
+        <v>35.5</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9929078014184396</v>
+        <v>0.9859154929577464</v>
       </c>
       <c r="J128" t="n">
         <v>-3</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>2.755000114440918</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3629763914557708</v>
+        <v>0.3676470549564461</v>
       </c>
       <c r="J130" t="n">
         <v>-3</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>21.67000007629395</v>
+        <v>21.68000030517578</v>
       </c>
       <c r="I131" t="n">
-        <v>5.168435607091816</v>
+        <v>5.166051587797333</v>
       </c>
       <c r="J131" t="n">
         <v>-3</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>1.450000047683716</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I132" t="n">
-        <v>6.896551497342619</v>
+        <v>6.756756669679118</v>
       </c>
       <c r="J132" t="n">
         <v>-3</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.309999942779541</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I134" t="n">
-        <v>3.995671094646811</v>
+        <v>4.120535696742638</v>
       </c>
       <c r="J134" t="n">
         <v>-3</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>9.020000457763672</v>
+        <v>8.960000038146973</v>
       </c>
       <c r="I135" t="n">
-        <v>3.880265878465104</v>
+        <v>3.906249983369239</v>
       </c>
       <c r="J135" t="n">
         <v>-10</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.079999923706055</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6607929570941081</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J139" t="n">
         <v>-10</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>18.89999961853027</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I140" t="n">
-        <v>2.64550269889837</v>
+        <v>2.673796682355883</v>
       </c>
       <c r="J140" t="n">
         <v>-10</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>15.18000030517578</v>
+        <v>15.19999980926514</v>
       </c>
       <c r="I142" t="n">
-        <v>3.293807575415659</v>
+        <v>3.289473725487982</v>
       </c>
       <c r="J142" t="n">
         <v>-10</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.579999923706055</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="I143" t="n">
-        <v>2.79329614891385</v>
+        <v>2.777777851363761</v>
       </c>
       <c r="J143" t="n">
         <v>-10</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.049999952316284</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="I144" t="n">
-        <v>3.606557433434118</v>
+        <v>3.642384128964558</v>
       </c>
       <c r="J144" t="n">
         <v>-10</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>4.880000114440918</v>
+        <v>4.809999942779541</v>
       </c>
       <c r="I146" t="n">
-        <v>1.946721265822835</v>
+        <v>1.975051998547481</v>
       </c>
       <c r="J146" t="n">
         <v>-10</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>1.210000038146973</v>
+        <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>2.479338764810522</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>-10</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>8.199999809265137</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I148" t="n">
-        <v>1.097561001139408</v>
+        <v>1.104294530215329</v>
       </c>
       <c r="J148" t="n">
         <v>-10</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>7.130000114440918</v>
+        <v>7.090000152587891</v>
       </c>
       <c r="I150" t="n">
-        <v>3.085553947669898</v>
+        <v>3.102961851414047</v>
       </c>
       <c r="J150" t="n">
         <v>-10</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>27.35000038146973</v>
+        <v>28.20000076293945</v>
       </c>
       <c r="I151" t="n">
-        <v>2.230347318069105</v>
+        <v>2.163120508853547</v>
       </c>
       <c r="J151" t="n">
         <v>-17</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>2.819999933242798</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I152" t="n">
-        <v>5.319149062089187</v>
+        <v>5.226481044642261</v>
       </c>
       <c r="J152" t="n">
         <v>-17</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.80000019073486</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="I153" t="n">
-        <v>5.932203293942543</v>
+        <v>6.11353721974364</v>
       </c>
       <c r="J153" t="n">
         <v>-17</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>8.869999885559082</v>
+        <v>8.840000152587891</v>
       </c>
       <c r="I154" t="n">
-        <v>5.755355203906215</v>
+        <v>5.774886778147308</v>
       </c>
       <c r="J154" t="n">
         <v>-17</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>8.609999656677246</v>
+        <v>8.5</v>
       </c>
       <c r="I155" t="n">
-        <v>3.135888626785357</v>
+        <v>3.176470588235294</v>
       </c>
       <c r="J155" t="n">
         <v>-17</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>6.65500020980835</v>
+        <v>6.590000152587891</v>
       </c>
       <c r="I156" t="n">
-        <v>5.259203440507168</v>
+        <v>5.3110772670097</v>
       </c>
       <c r="J156" t="n">
         <v>-17</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>42</v>
+        <v>42.40000152587891</v>
       </c>
       <c r="I157" t="n">
-        <v>2.619047619047619</v>
+        <v>2.594339529277171</v>
       </c>
       <c r="J157" t="n">
         <v>-17</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>16.95000076293945</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="I158" t="n">
-        <v>4.424778561897455</v>
+        <v>4.437869922657575</v>
       </c>
       <c r="J158" t="n">
         <v>-17</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>10.39999961853027</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I159" t="n">
-        <v>4.134615536272179</v>
+        <v>4.174757204245461</v>
       </c>
       <c r="J159" t="n">
         <v>-17</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>4.340000152587891</v>
+        <v>4.324999809265137</v>
       </c>
       <c r="I160" t="n">
-        <v>3.456221076641133</v>
+        <v>3.468208245435428</v>
       </c>
       <c r="J160" t="n">
         <v>-17</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>11.81999969482422</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I161" t="n">
-        <v>1.668096489768414</v>
+        <v>1.670923701804796</v>
       </c>
       <c r="J161" t="n">
         <v>-17</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>29.60000038146973</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I162" t="n">
-        <v>3.716216168323515</v>
+        <v>3.75426630936102</v>
       </c>
       <c r="J162" t="n">
         <v>-17</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>67.19999694824219</v>
+        <v>65.30000305175781</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6994047936668756</v>
+        <v>0.7197549433917646</v>
       </c>
       <c r="J163" t="n">
         <v>-17</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>86.80000305175781</v>
+        <v>86.19999694824219</v>
       </c>
       <c r="I164" t="n">
-        <v>1.382488430656453</v>
+        <v>1.392111418194743</v>
       </c>
       <c r="J164" t="n">
         <v>-17</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>22.75</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I165" t="n">
-        <v>1.186813186813187</v>
+        <v>1.192053000208924</v>
       </c>
       <c r="J165" t="n">
         <v>-17</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>10.14999961853027</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I166" t="n">
-        <v>3.743842505237692</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J166" t="n">
         <v>-17</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>33.25</v>
+        <v>33.15000152587891</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9022556390977442</v>
+        <v>0.9049773339099297</v>
       </c>
       <c r="J167" t="n">
         <v>-17</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>0.1687999963760376</v>
+        <v>0.1695999950170517</v>
       </c>
       <c r="I168" t="n">
-        <v>4.146919520309718</v>
+        <v>4.127358611830275</v>
       </c>
       <c r="J168" t="n">
         <v>-24</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>6.78000020980835</v>
+        <v>6.789999961853027</v>
       </c>
       <c r="I169" t="n">
-        <v>2.359881932872724</v>
+        <v>2.356406493356373</v>
       </c>
       <c r="J169" t="n">
         <v>-24</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>2.069999933242798</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I170" t="n">
-        <v>3.140096719625155</v>
+        <v>3.155339893470873</v>
       </c>
       <c r="J170" t="n">
         <v>-24</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>8.279999732971191</v>
+        <v>8.229999542236328</v>
       </c>
       <c r="I171" t="n">
-        <v>3.019323768870342</v>
+        <v>3.037667240648081</v>
       </c>
       <c r="J171" t="n">
         <v>-24</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>1.309999942779541</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="I172" t="n">
-        <v>5.34351168378488</v>
+        <v>5.223880466891178</v>
       </c>
       <c r="J172" t="n">
         <v>-24</v>
@@ -10433,44 +10433,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>